--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,12 +73,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>班尼迪克</t>
   </si>
 </sst>
 </file>
@@ -504,25 +499,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,10 @@
   </si>
   <si>
     <t>班尼迪克</t>
+  </si>
+  <si>
+    <t>测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -516,6 +520,9 @@
       <c r="G4" s="1">
         <v>2</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3">

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,22 +61,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>beginCoordinate:int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>班尼迪克</t>
   </si>
   <si>
     <t>测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beginCoordinate</t>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>-10,12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -123,11 +140,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -435,18 +455,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:H4"/>
+  <dimension ref="A2:G6"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="7" width="16.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="7.75" style="1"/>
+    <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -462,17 +483,14 @@
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -488,19 +506,16 @@
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B4" s="1">
         <v>3000</v>
@@ -512,16 +527,59 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1" t="s">
+        <v>-1000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-1000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>948</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,6 +94,17 @@
   </si>
   <si>
     <t>-10,12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-50,20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -455,7 +466,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G6"/>
+  <dimension ref="A2:G7"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -580,6 +591,29 @@
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>948</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,10 +86,6 @@
     <t>beginCoordinate</t>
   </si>
   <si>
-    <t>2,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2,3</t>
   </si>
   <si>
@@ -105,6 +101,14 @@
   </si>
   <si>
     <t>-50,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +530,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1">
         <v>3000</v>
@@ -538,13 +542,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>-1000</v>
+        <v>1014</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -564,7 +568,7 @@
         <v>-1000</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
@@ -587,7 +591,7 @@
         <v>948</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -595,7 +599,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1">
         <v>2001</v>
@@ -610,10 +614,10 @@
         <v>948</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -109,6 +109,20 @@
   </si>
   <si>
     <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
+  </si>
+  <si>
+    <t>-60,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-68,15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -470,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G7"/>
+  <dimension ref="A2:G9"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -618,6 +632,52 @@
       </c>
       <c r="G7" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>900</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>900</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,21 @@
   <si>
     <t>-68,15</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>dailyTasks</t>
+  </si>
+  <si>
+    <t>beds</t>
+  </si>
+  <si>
+    <t>workItems</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
   </si>
 </sst>
 </file>
@@ -484,7 +499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -492,11 +507,11 @@
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
     <col min="8" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -518,8 +533,17 @@
       <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -541,8 +565,17 @@
       <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -565,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -588,7 +621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -611,7 +644,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -634,7 +667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -657,7 +690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,6 +139,46 @@
   </si>
   <si>
     <t>List&lt;int2&gt;</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1070089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1071156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014,1089143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1081513</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1080132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1079546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1079546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -508,10 +548,12 @@
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="7.75" style="1"/>
+    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="16.625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -536,14 +578,14 @@
       <c r="H2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -568,10 +610,10 @@
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -597,6 +639,12 @@
       <c r="G4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
@@ -643,6 +691,15 @@
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
@@ -666,6 +723,15 @@
       <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
@@ -689,6 +755,15 @@
       <c r="G8" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
@@ -711,6 +786,15 @@
       </c>
       <c r="G9" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,58 +57,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>behaviorName</t>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beginCoordinate</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>-10,12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-50,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44,33</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>班尼迪克</t>
-  </si>
-  <si>
-    <t>测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>beginCoordinate</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>-10,12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-50,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>44,33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班尼迪克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -123,61 +106,6 @@
   </si>
   <si>
     <t>-68,15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>dailyTasks</t>
-  </si>
-  <si>
-    <t>beds</t>
-  </si>
-  <si>
-    <t>workItems</t>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1070089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1071156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014,1089143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1081513</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1080132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1079546</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1079546</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +467,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J9"/>
+  <dimension ref="A2:F9"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -547,13 +475,10 @@
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="16.625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="7.75" style="1"/>
+    <col min="7" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -570,22 +495,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -602,24 +515,12 @@
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>3000</v>
@@ -634,21 +535,12 @@
         <v>1014</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>3001</v>
@@ -663,15 +555,12 @@
         <v>-1000</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>2000</v>
@@ -686,24 +575,12 @@
         <v>948</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
         <v>2001</v>
@@ -718,24 +595,12 @@
         <v>948</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="B8" s="1">
         <v>2002</v>
@@ -750,24 +615,12 @@
         <v>900</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1">
         <v>2003</v>
@@ -782,19 +635,7 @@
         <v>900</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,146 @@
   </si>
   <si>
     <t>-68,15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10,45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-17,26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>教堂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>0,37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>0,23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>15,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>-20,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>0,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhangp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>-4,16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>村公所卧室</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>0,9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼摊内部</t>
+  </si>
+  <si>
+    <t>-8,-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>治安室</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>23,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>-6,-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器店</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>-27,16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>-8,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -161,6 +301,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,7 +610,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:F9"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -478,7 +621,7 @@
     <col min="7" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -498,7 +641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -518,7 +661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -538,7 +681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -558,7 +701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -578,7 +721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -598,7 +741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -618,7 +761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -636,6 +779,182 @@
       </c>
       <c r="F9" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -109,14 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>-10,45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-17,26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>琼</t>
   </si>
   <si>
@@ -126,14 +118,6 @@
     <t>坎蒂丝</t>
   </si>
   <si>
-    <t>教堂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家具店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -152,10 +136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>酒馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黛芙妮</t>
   </si>
   <si>
@@ -177,10 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zhangp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>梅林</t>
   </si>
   <si>
@@ -195,9 +171,6 @@
     <t>帕特里克</t>
   </si>
   <si>
-    <t>村公所卧室</t>
-  </si>
-  <si>
     <t>摩尔根</t>
   </si>
   <si>
@@ -205,9 +178,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>鱼摊内部</t>
-  </si>
-  <si>
     <t>-8,-11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -215,45 +185,207 @@
     <t>瓦尔特</t>
   </si>
   <si>
-    <t>治安室</t>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>-6,-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>-27,16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>-8,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>阿普敦</t>
-  </si>
-  <si>
-    <t>23,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>-6,-10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器店</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>-27,16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>-8,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-26,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-13,37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+  </si>
+  <si>
+    <t>马</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>莎拉</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>杰克</t>
+  </si>
+  <si>
+    <t>黛娜</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>npcName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +398,13 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -292,7 +431,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -305,6 +444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -610,7 +750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G25"/>
+  <dimension ref="A2:F37"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -621,7 +761,7 @@
     <col min="7" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -641,7 +781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -661,7 +801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -669,6 +809,7 @@
         <v>3000</v>
       </c>
       <c r="C4" s="1">
+        <f>VLOOKUP(A4,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>3</v>
       </c>
       <c r="D4" s="1" t="b">
@@ -681,7 +822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -689,6 +830,7 @@
         <v>3001</v>
       </c>
       <c r="C5" s="1">
+        <f>VLOOKUP(A5,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>4</v>
       </c>
       <c r="D5" s="1" t="b">
@@ -701,7 +843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -709,6 +851,7 @@
         <v>2000</v>
       </c>
       <c r="C6" s="1">
+        <f>VLOOKUP(A6,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>6</v>
       </c>
       <c r="D6" s="1" t="b">
@@ -721,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -729,6 +872,7 @@
         <v>2001</v>
       </c>
       <c r="C7" s="1">
+        <f>VLOOKUP(A7,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="D7" s="1" t="b">
@@ -741,7 +885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -749,6 +893,7 @@
         <v>2002</v>
       </c>
       <c r="C8" s="1">
+        <f>VLOOKUP(A8,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="D8" s="1" t="b">
@@ -761,7 +906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -769,6 +914,7 @@
         <v>2003</v>
       </c>
       <c r="C9" s="1">
+        <f>VLOOKUP(A9,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="b">
@@ -781,182 +927,574 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C10" s="1">
+        <f>VLOOKUP(A10,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5170</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C11" s="1">
+        <f>VLOOKUP(A11,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5170</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C12" s="1">
+        <f>VLOOKUP(A12,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1014</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C13" s="1">
+        <f>VLOOKUP(A13,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>17</v>
+      </c>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1014</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="B14" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C14" s="1">
+        <f>VLOOKUP(A14,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2180</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C15" s="1">
+        <f>VLOOKUP(A15,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="D15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2180</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C16" s="1">
+        <f>VLOOKUP(A16,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>36</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2180</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C17" s="1">
+        <f>VLOOKUP(A17,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="D17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3056</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C18" s="1">
+        <f>VLOOKUP(A18,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3056</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C19" s="1">
+        <f>VLOOKUP(A19,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2015</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C20" s="1">
+        <f>VLOOKUP(A20,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>26</v>
+      </c>
+      <c r="D20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2902</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C21" s="1">
+        <f>VLOOKUP(A21,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="D21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1912</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C22" s="1">
+        <f>VLOOKUP(A22,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1756</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C23" s="1">
+        <f>VLOOKUP(A23,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1756</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C24" s="1">
+        <f>VLOOKUP(A24,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>39</v>
+      </c>
+      <c r="D24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1912</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C25" s="1">
+        <f>VLOOKUP(A25,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>5170</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C26" s="1">
+        <f>VLOOKUP(A26,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4800</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C27" s="1">
+        <f>VLOOKUP(A27,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4918</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C28" s="1">
+        <f>VLOOKUP(A28,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>5013</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C29" s="1">
+        <f>VLOOKUP(A29,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>5013</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C30" s="1">
+        <f>VLOOKUP(A30,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>21</v>
+      </c>
+      <c r="D30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3300</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="1">
+        <f>VLOOKUP(A31,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>24</v>
+      </c>
+      <c r="D31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>4765</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="1">
+        <f>VLOOKUP(A32,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>35</v>
+      </c>
+      <c r="D32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4696</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2027</v>
+      </c>
+      <c r="C33" s="1">
+        <f>VLOOKUP(A33,Sheet1!$E$16:$F$55,2,FALSE)</f>
+        <v>28</v>
+      </c>
+      <c r="D33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>5476</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2028</v>
+      </c>
+      <c r="C34" s="1">
+        <f>VLOOKUP(A34,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="D34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>5476</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2029</v>
+      </c>
+      <c r="C35" s="1">
+        <f>VLOOKUP(A35,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="D35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5293</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2030</v>
+      </c>
+      <c r="C36" s="1">
+        <f>VLOOKUP(A36,Sheet1!$E$16:$F$55,2,FALSE)</f>
         <v>41</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
+      <c r="D36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>5309</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A3:C3">
     <sortState ref="A4:K127">
@@ -972,9 +1510,330 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1"/>
+  <dimension ref="E16:F55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="16" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E35" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E42" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E43" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E47" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E51" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E52" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E54" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.15">
+      <c r="E55" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Datas/MapNpcData.xlsx
+++ b/Datas/MapNpcData.xlsx
@@ -294,10 +294,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,36</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -379,6 +375,10 @@
   <si>
     <t>npcName</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -750,7 +750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:F37"/>
+  <dimension ref="A2:F36"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -1428,7 +1428,7 @@
         <v>5476</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1449,7 +1449,7 @@
         <v>5476</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1475,7 +1475,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1">
         <v>2030</v>
@@ -1491,10 +1491,9 @@
         <v>5309</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:C3">
     <sortState ref="A4:K127">
@@ -1515,15 +1514,15 @@
   <sheetData>
     <row r="16" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -1531,7 +1530,7 @@
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -1539,7 +1538,7 @@
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1547,7 +1546,7 @@
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -1571,7 +1570,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23">
         <v>9</v>
@@ -1587,7 +1586,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F25">
         <v>11</v>
@@ -1595,7 +1594,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26">
         <v>12</v>
@@ -1603,7 +1602,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F27">
         <v>13</v>
@@ -1619,7 +1618,7 @@
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29">
         <v>15</v>
@@ -1643,7 +1642,7 @@
     </row>
     <row r="32" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32">
         <v>18</v>
@@ -1659,7 +1658,7 @@
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F34">
         <v>20</v>
@@ -1667,7 +1666,7 @@
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F35">
         <v>21</v>
@@ -1691,7 +1690,7 @@
     </row>
     <row r="38" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38">
         <v>24</v>
@@ -1715,7 +1714,7 @@
     </row>
     <row r="41" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F41">
         <v>27</v>
@@ -1723,7 +1722,7 @@
     </row>
     <row r="42" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42">
         <v>28</v>
@@ -1731,7 +1730,7 @@
     </row>
     <row r="43" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F43">
         <v>29</v>
@@ -1739,7 +1738,7 @@
     </row>
     <row r="44" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F44">
         <v>30</v>
@@ -1755,7 +1754,7 @@
     </row>
     <row r="46" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F46">
         <v>32</v>
@@ -1763,7 +1762,7 @@
     </row>
     <row r="47" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F47">
         <v>33</v>
@@ -1779,7 +1778,7 @@
     </row>
     <row r="49" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F49">
         <v>35</v>
@@ -1803,7 +1802,7 @@
     </row>
     <row r="52" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F52">
         <v>38</v>
@@ -1827,7 +1826,7 @@
     </row>
     <row r="55" spans="5:6" x14ac:dyDescent="0.15">
       <c r="E55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F55">
         <v>41</v>
